--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486696_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486696_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. DAMIAN</t>
+          <t>E. QUIJADA GARCÍA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5171</v>
+        <v>0.3243</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.3591</v>
+        <v>-0.2446</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8762</v>
+        <v>0.5689</v>
       </c>
       <c r="G2" t="n">
-        <v>1.9033</v>
+        <v>0.7519</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.9241</v>
+        <v>-1.1313</v>
       </c>
       <c r="I2" t="n">
-        <v>3.8274</v>
+        <v>1.8832</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9184</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.7508</v>
+        <v>-0.6481</v>
       </c>
       <c r="L2" t="n">
-        <v>3.6692</v>
+        <v>1.1869</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.0151</v>
+        <v>0.2131</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.1733</v>
+        <v>-0.4832</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1582</v>
+        <v>0.6962</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.3515</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.8962</v>
+        <v>-0.9654</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5446</v>
+        <v>0.9654</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7446</v>
+        <v>0.1862</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2752</v>
+        <v>-0.1037</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4694</v>
+        <v>0.2899</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.7792</v>
+        <v>-0.6138</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.6565</v>
+        <v>0.2856</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1228</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. THIAW</t>
+          <t>D. DAMIAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1573</v>
+        <v>0.1448</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3062</v>
+        <v>-0.6072</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1489</v>
+        <v>0.752</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1889</v>
+        <v>1.9033</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1867</v>
+        <v>-1.9241</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0022</v>
+        <v>3.8274</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3283</v>
+        <v>2.9184</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0842</v>
+        <v>-0.7508</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2442</v>
+        <v>3.6692</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1395</v>
+        <v>-1.0151</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8975</v>
+        <v>-1.1733</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.242</v>
+        <v>0.1582</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.5792</v>
+        <v>-1.3515</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9308</v>
+        <v>-2.8962</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3515</v>
+        <v>1.5446</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9987</v>
+        <v>0.3723</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2764</v>
+        <v>0.0271</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2751</v>
+        <v>0.3452</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.451</v>
+        <v>-0.7792</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1851</v>
+        <v>-0.6565</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.6361</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. QUIJADA GARCÍA</t>
+          <t>M. THIAW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0218</v>
+        <v>-0.0414</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6652</v>
+        <v>0.6786</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6434</v>
+        <v>-0.7201</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7519</v>
+        <v>0.1889</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1313</v>
+        <v>0.1867</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8832</v>
+        <v>0.0022</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5387999999999999</v>
+        <v>1.3283</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6481</v>
+        <v>1.0842</v>
       </c>
       <c r="L4" t="n">
-        <v>1.1869</v>
+        <v>0.2442</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2131</v>
+        <v>-1.1395</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4832</v>
+        <v>-0.8975</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6962</v>
+        <v>-0.242</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9654</v>
+        <v>1.3515</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1599</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5243</v>
+        <v>0.096</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3644</v>
+        <v>0.7039</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6138</v>
+        <v>-0.451</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2856</v>
+        <v>1.1851</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8995</v>
+        <v>-1.6361</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0318</v>
+        <v>-1.1169</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2413</v>
+        <v>0.0072</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2731</v>
+        <v>-1.1241</v>
       </c>
       <c r="G5" t="n">
         <v>-1.0106</v>
@@ -844,13 +844,13 @@
         <v>1.7377</v>
       </c>
       <c r="S5" t="n">
-        <v>1.9745</v>
+        <v>0.8893</v>
       </c>
       <c r="T5" t="n">
-        <v>1.599</v>
+        <v>0.3649</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3755</v>
+        <v>0.5245</v>
       </c>
       <c r="V5" t="n">
         <v>0.1628</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3876</v>
+        <v>-1.3131</v>
       </c>
       <c r="E6" t="n">
         <v>-0.8136</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.574</v>
+        <v>-0.4995</v>
       </c>
       <c r="G6" t="n">
         <v>-0.5725</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5296</v>
+        <v>-0.4551</v>
       </c>
       <c r="T6" t="n">
         <v>-0.1655</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.364</v>
+        <v>-0.2895</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2856</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. LOPEZ ROMERA</t>
+          <t>M. MELERO JAREÑO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.0211</v>
+        <v>-1.7426</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8712</v>
+        <v>0.0336</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1498</v>
+        <v>-1.7762</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.7199</v>
+        <v>-1.3673</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-0.628</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.0783</v>
+        <v>-0.7392</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9812</v>
+        <v>-0.2904</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2963</v>
+        <v>-0.2136</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6849</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7387</v>
+        <v>-1.0769</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3453</v>
+        <v>-0.4145</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3934</v>
+        <v>-0.6624</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7723</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7723</v>
+        <v>0.9654</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1542</v>
+        <v>-0.0897</v>
       </c>
       <c r="T7" t="n">
-        <v>0.11</v>
+        <v>0.0616</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0442</v>
+        <v>-0.1514</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2277</v>
+        <v>-0.2856</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2277</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. MELERO JAREÑO</t>
+          <t>A. LOPEZ ROMERA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.5962</v>
+        <v>-1.8996</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7456</v>
+        <v>-1.0229</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.8507</v>
+        <v>-0.8767</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3673</v>
+        <v>-1.7199</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.628</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7392</v>
+        <v>-1.0783</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2904</v>
+        <v>-0.9812</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2136</v>
+        <v>-0.2963</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.6849</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0769</v>
+        <v>-0.7387</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4145</v>
+        <v>-0.3453</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6624</v>
+        <v>-0.3934</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.7723</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9654</v>
+        <v>0.7723</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9434</v>
+        <v>0.2757</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7175</v>
+        <v>-0.0417</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2259</v>
+        <v>0.3174</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2856</v>
+        <v>-1.2277</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.5133</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1298</v>
+        <v>-3.105</v>
       </c>
       <c r="E9" t="n">
         <v>-0.8895</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.2403</v>
+        <v>-2.2154</v>
       </c>
       <c r="G9" t="n">
         <v>-1.9034</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2042</v>
+        <v>-0.1793</v>
       </c>
       <c r="T9" t="n">
         <v>-0.2207</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0166</v>
+        <v>0.0414</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0222</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.1174</v>
+        <v>-4.7808</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.726</v>
+        <v>-4.464</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3913</v>
+        <v>-0.3168</v>
       </c>
       <c r="G10" t="n">
         <v>-4.4027</v>
@@ -1234,13 +1234,13 @@
         <v>1.3515</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.495</v>
+        <v>-1.1584</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8554</v>
+        <v>-0.5934</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6395999999999999</v>
+        <v>-0.5651</v>
       </c>
       <c r="V10" t="n">
         <v>-0.5712</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.899699999999999</v>
+        <v>-8.1729</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.4215</v>
+        <v>-6.794</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4782</v>
+        <v>-1.3789</v>
       </c>
       <c r="G11" t="n">
         <v>-6.0394</v>
@@ -1312,13 +1312,13 @@
         <v>0.9654</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0924</v>
+        <v>-0.3656</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7451</v>
+        <v>-0.1177</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3472</v>
+        <v>-0.2479</v>
       </c>
       <c r="V11" t="n">
         <v>0.1628</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-22.531</v>
+        <v>-21.7032</v>
       </c>
       <c r="E12" t="n">
-        <v>-14.9442</v>
+        <v>-14.1164</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.5867</v>
+        <v>-7.586799999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-14.1717</v>
@@ -1360,7 +1360,7 @@
         <v>-7.9326</v>
       </c>
       <c r="I12" t="n">
-        <v>-6.238999999999999</v>
+        <v>-6.239000000000001</v>
       </c>
       <c r="J12" t="n">
         <v>-4.7142</v>
@@ -1369,7 +1369,7 @@
         <v>-1.03</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.684099999999999</v>
+        <v>-3.6841</v>
       </c>
       <c r="M12" t="n">
         <v>-9.457699999999999</v>
@@ -1390,19 +1390,19 @@
         <v>9.6538</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5524999999999998</v>
+        <v>0.2753</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.5207</v>
+        <v>-0.6931000000000002</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9685000000000001</v>
+        <v>0.9683999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-4.9107</v>
       </c>
       <c r="W12" t="n">
-        <v>3.8408</v>
+        <v>3.840800000000001</v>
       </c>
       <c r="X12" t="n">
         <v>-8.7517</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.8528</v>
+        <v>7.8516</v>
       </c>
       <c r="E13" t="n">
-        <v>4.8527</v>
+        <v>4.1287</v>
       </c>
       <c r="F13" t="n">
-        <v>3.0001</v>
+        <v>3.7229</v>
       </c>
       <c r="G13" t="n">
         <v>3.6173</v>
@@ -1468,13 +1468,13 @@
         <v>2.51</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1161</v>
+        <v>-0.1172</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5236</v>
+        <v>-0.2004</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6395999999999999</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>1.8415</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.4639</v>
+        <v>6.8376</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0029</v>
+        <v>3.3132</v>
       </c>
       <c r="F14" t="n">
-        <v>3.4611</v>
+        <v>3.5245</v>
       </c>
       <c r="G14" t="n">
         <v>3.2403</v>
@@ -1546,13 +1546,13 @@
         <v>1.5446</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4908</v>
+        <v>-0.1171</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6898</v>
+        <v>-0.3796</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1991</v>
+        <v>0.2625</v>
       </c>
       <c r="V14" t="n">
         <v>2.1698</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.5952</v>
+        <v>5.2805</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8568</v>
+        <v>3.167</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7384</v>
+        <v>2.1135</v>
       </c>
       <c r="G15" t="n">
         <v>3.0665</v>
@@ -1624,13 +1624,13 @@
         <v>1.5446</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5405</v>
+        <v>0.1448</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3864</v>
+        <v>-0.0761</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1542</v>
+        <v>0.221</v>
       </c>
       <c r="V15" t="n">
         <v>2.4554</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.348</v>
+        <v>4.1176</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9323</v>
+        <v>2.1391</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4158</v>
+        <v>1.9784</v>
       </c>
       <c r="G16" t="n">
         <v>1.5629</v>
@@ -1702,13 +1702,13 @@
         <v>0.9654</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1489</v>
+        <v>0.6206</v>
       </c>
       <c r="T16" t="n">
-        <v>0.11</v>
+        <v>0.3169</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2589</v>
+        <v>0.3037</v>
       </c>
       <c r="V16" t="n">
         <v>2.1271</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8233</v>
+        <v>1.5846</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1814</v>
+        <v>-0.2848</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0047</v>
+        <v>1.8694</v>
       </c>
       <c r="G17" t="n">
         <v>0.5077</v>
@@ -1780,13 +1780,13 @@
         <v>0.9654</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1145</v>
+        <v>0.8758</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0825</v>
+        <v>-0.0209</v>
       </c>
       <c r="U17" t="n">
-        <v>1.032</v>
+        <v>0.8968</v>
       </c>
       <c r="V17" t="n">
         <v>-0.5712</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2769</v>
+        <v>1.3017</v>
       </c>
       <c r="E18" t="n">
         <v>-0.5941</v>
       </c>
       <c r="F18" t="n">
-        <v>1.871</v>
+        <v>1.8959</v>
       </c>
       <c r="G18" t="n">
         <v>0.0467</v>
@@ -1858,13 +1858,13 @@
         <v>1.1585</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0717</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="T18" t="n">
         <v>-0.4139</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4857</v>
+        <v>0.5105</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1701</v>
+        <v>1.1175</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9644</v>
+        <v>-0.7575</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1344</v>
+        <v>1.875</v>
       </c>
       <c r="G19" t="n">
         <v>1.9335</v>
@@ -1936,13 +1936,13 @@
         <v>1.1585</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2872</v>
+        <v>0.2346</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5243</v>
+        <v>-0.3174</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8115</v>
+        <v>0.5521</v>
       </c>
       <c r="V19" t="n">
         <v>-0.0852</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9362</v>
+        <v>0.7609</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5362</v>
+        <v>-0.6397</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4725</v>
+        <v>1.4006</v>
       </c>
       <c r="G20" t="n">
         <v>0.8011</v>
@@ -2014,13 +2014,13 @@
         <v>0.9654</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7063</v>
+        <v>0.5311</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3307</v>
+        <v>0.2273</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3756</v>
+        <v>0.3037</v>
       </c>
       <c r="V20" t="n">
         <v>-0.5712</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4249</v>
+        <v>-0.4001</v>
       </c>
       <c r="E21" t="n">
         <v>-0.1655</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2594</v>
+        <v>-0.2346</v>
       </c>
       <c r="G21" t="n">
         <v>-0.2759</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.149</v>
+        <v>-0.1242</v>
       </c>
       <c r="T21" t="n">
         <v>-0.1655</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0166</v>
+        <v>0.0414</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7010999999999999</v>
+        <v>-0.9851</v>
       </c>
       <c r="E22" t="n">
-        <v>2.2296</v>
+        <v>1.609</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.9307</v>
+        <v>-2.5942</v>
       </c>
       <c r="G22" t="n">
         <v>2.8356</v>
@@ -2170,13 +2170,13 @@
         <v>0.3862</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6564</v>
+        <v>0.3724</v>
       </c>
       <c r="T22" t="n">
-        <v>0.7995</v>
+        <v>0.179</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1431</v>
+        <v>0.1934</v>
       </c>
       <c r="V22" t="n">
         <v>-2.4554</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8094</v>
+        <v>-2.8675</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.8457</v>
+        <v>-4.3286</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0363</v>
+        <v>1.4611</v>
       </c>
       <c r="G23" t="n">
         <v>-3.164</v>
@@ -2248,13 +2248,13 @@
         <v>1.3515</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8384</v>
+        <v>0.1035</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6347</v>
+        <v>-0.1175</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2038</v>
+        <v>0.221</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>22.531</v>
+        <v>24.5993</v>
       </c>
       <c r="E24" t="n">
-        <v>7.586999999999999</v>
+        <v>7.586800000000002</v>
       </c>
       <c r="F24" t="n">
-        <v>14.9442</v>
+        <v>17.0125</v>
       </c>
       <c r="G24" t="n">
         <v>14.1717</v>
@@ -2326,13 +2326,13 @@
         <v>12.5501</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5524000000000004</v>
+        <v>2.6209</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9683</v>
+        <v>-0.9680999999999997</v>
       </c>
       <c r="U24" t="n">
-        <v>1.5209</v>
+        <v>3.5892</v>
       </c>
       <c r="V24" t="n">
         <v>4.910799999999999</v>
